--- a/results/01_compounds_all.xlsx
+++ b/results/01_compounds_all.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
   <si>
     <t xml:space="preserve">Medicinal.materials(Latin.name)</t>
   </si>
@@ -29,10 +29,13 @@
     <t xml:space="preserve">CID</t>
   </si>
   <si>
+    <t xml:space="preserve">Compound_Count</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source</t>
   </si>
   <si>
-    <t xml:space="preserve">Aconitum carmichaeli</t>
+    <t xml:space="preserve">Aconitum carmichaeli Debeaux</t>
   </si>
   <si>
     <t xml:space="preserve">FU ZI</t>
@@ -41,81 +44,126 @@
     <t xml:space="preserve">talatisamine</t>
   </si>
   <si>
+    <t xml:space="preserve">C24H39NO5</t>
+  </si>
+  <si>
     <t xml:space="preserve">159891</t>
   </si>
   <si>
+    <t xml:space="preserve">DCABM-TCM; Tan-2012-in vivo; Zhang-2024-in vivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neoline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesaconitine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C33H45NO11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">441747</t>
+  </si>
+  <si>
     <t xml:space="preserve">DCABM-TCM</t>
   </si>
   <si>
-    <t xml:space="preserve">neoline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mesaconitine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">441747</t>
-  </si>
-  <si>
     <t xml:space="preserve">hypaconitine</t>
   </si>
   <si>
+    <t xml:space="preserve">C33H45NO10</t>
+  </si>
+  <si>
     <t xml:space="preserve">441737</t>
   </si>
   <si>
     <t xml:space="preserve">benzoylmesaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C31H43NO10</t>
+  </si>
+  <si>
     <t xml:space="preserve">24832659</t>
   </si>
   <si>
     <t xml:space="preserve">benzoylaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C32H45NO10</t>
+  </si>
+  <si>
     <t xml:space="preserve">20055771</t>
   </si>
   <si>
+    <t xml:space="preserve">DCABM-TCM; Tan-2012-in vivo</t>
+  </si>
+  <si>
     <t xml:space="preserve">acetyltalatisamine</t>
   </si>
   <si>
+    <t xml:space="preserve">C26H41NO6</t>
+  </si>
+  <si>
     <t xml:space="preserve">101596809</t>
   </si>
   <si>
     <t xml:space="preserve">benzoylhypaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C31H43NO9</t>
+  </si>
+  <si>
     <t xml:space="preserve">78358526</t>
   </si>
   <si>
     <t xml:space="preserve">senbusine c</t>
   </si>
   <si>
+    <t xml:space="preserve">C24H39NO7</t>
+  </si>
+  <si>
     <t xml:space="preserve">14163819</t>
   </si>
   <si>
     <t xml:space="preserve">toroko base ii</t>
   </si>
   <si>
+    <t xml:space="preserve">C25H41NO6</t>
+  </si>
+  <si>
     <t xml:space="preserve">20055812</t>
   </si>
   <si>
     <t xml:space="preserve">glucuronide conjugation of fuziline</t>
   </si>
   <si>
+    <t xml:space="preserve">C30H47NO13</t>
+  </si>
+  <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
     <t xml:space="preserve">songorine</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H31NO3</t>
+  </si>
+  <si>
     <t xml:space="preserve">71456946</t>
   </si>
   <si>
     <t xml:space="preserve">senbusine b</t>
   </si>
   <si>
+    <t xml:space="preserve">C23H37NO6</t>
+  </si>
+  <si>
     <t xml:space="preserve">senbusine a</t>
   </si>
   <si>
@@ -125,12 +173,18 @@
     <t xml:space="preserve">6,16,18-trimethoxy-13-(methoxymethyl)-11-methyl-11-azahexacyclo[7.7.2.12,5.01,10.03,8.013,17]nonadecane-4,5,7,8,14-pentol</t>
   </si>
   <si>
+    <t xml:space="preserve">C24H39NO9</t>
+  </si>
+  <si>
     <t xml:space="preserve">76189547</t>
   </si>
   <si>
     <t xml:space="preserve">aconitine</t>
   </si>
   <si>
+    <t xml:space="preserve">C34H47NO11</t>
+  </si>
+  <si>
     <t xml:space="preserve">245005</t>
   </si>
   <si>
@@ -143,18 +197,27 @@
     <t xml:space="preserve">sulfate conjugation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C25H41NO9S</t>
+  </si>
+  <si>
     <t xml:space="preserve">s-cysteine conjugation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C25H36N2O5S</t>
+  </si>
+  <si>
     <t xml:space="preserve">reduction of unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">reduction  of unknown</t>
+    <t xml:space="preserve">C31H45NO10</t>
   </si>
   <si>
     <t xml:space="preserve">methylation +sulfate conjugation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C24H39NO9S</t>
+  </si>
+  <si>
     <t xml:space="preserve">hydroxymethylene loss of unknown</t>
   </si>
   <si>
@@ -164,15 +227,27 @@
     <t xml:space="preserve">hydration of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C25H43NO7</t>
+  </si>
+  <si>
     <t xml:space="preserve">glycine conjugation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C27H44N2O7</t>
+  </si>
+  <si>
     <t xml:space="preserve">demethylation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C24H37NO9</t>
+  </si>
+  <si>
     <t xml:space="preserve">cysteine conjugation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C28H46N2O7S</t>
+  </si>
+  <si>
     <t xml:space="preserve">acetylation of unknown</t>
   </si>
   <si>
@@ -191,12 +266,18 @@
     <t xml:space="preserve">carmicheline</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H35NO4</t>
+  </si>
+  <si>
     <t xml:space="preserve">441742</t>
   </si>
   <si>
     <t xml:space="preserve">3-deoxyaconitine</t>
   </si>
   <si>
+    <t xml:space="preserve">C34H47NO10</t>
+  </si>
+  <si>
     <t xml:space="preserve">21598997</t>
   </si>
   <si>
@@ -209,6 +290,9 @@
     <t xml:space="preserve">20-ethyl-16-methoxy-4-(methoxymethyl)aconitane-1,8,14-triol</t>
   </si>
   <si>
+    <t xml:space="preserve">C23H37NO5</t>
+  </si>
+  <si>
     <t xml:space="preserve">3084020</t>
   </si>
   <si>
@@ -221,12 +305,21 @@
     <t xml:space="preserve">demethylated metabolite of isotalatizidine</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H35NO5</t>
+  </si>
+  <si>
     <t xml:space="preserve">dehydrated benzoylmesaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C31H41O9N</t>
+  </si>
+  <si>
     <t xml:space="preserve">dehydrated benzoylhypaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C31H41O8N</t>
+  </si>
+  <si>
     <t xml:space="preserve">cammaconine</t>
   </si>
   <si>
@@ -236,21 +329,33 @@
     <t xml:space="preserve">10-oh-mesaconitine</t>
   </si>
   <si>
+    <t xml:space="preserve">C33H45NO12</t>
+  </si>
+  <si>
     <t xml:space="preserve">78358536</t>
   </si>
   <si>
     <t xml:space="preserve">acetyltalatizamine</t>
   </si>
   <si>
+    <t xml:space="preserve">C26H41O6N</t>
+  </si>
+  <si>
     <t xml:space="preserve">10-oh-benzoylmesaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C31H43O11N</t>
+  </si>
+  <si>
     <t xml:space="preserve">isotalatisamine</t>
   </si>
   <si>
     <t xml:space="preserve">isodelphinine</t>
   </si>
   <si>
+    <t xml:space="preserve">C33H45NO9</t>
+  </si>
+  <si>
     <t xml:space="preserve">102146471</t>
   </si>
   <si>
@@ -263,6 +368,9 @@
     <t xml:space="preserve">jesaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C25H41NO9</t>
+  </si>
+  <si>
     <t xml:space="preserve">20054813</t>
   </si>
   <si>
@@ -275,9 +383,15 @@
     <t xml:space="preserve">3,13-deoxybenzoylaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C31H44NO8</t>
+  </si>
+  <si>
     <t xml:space="preserve">10-oh-benzoylaconine</t>
   </si>
   <si>
+    <t xml:space="preserve">C31H43NO11</t>
+  </si>
+  <si>
     <t xml:space="preserve">Astragalus membranaceus</t>
   </si>
   <si>
@@ -287,204 +401,312 @@
     <t xml:space="preserve">formononetin</t>
   </si>
   <si>
+    <t xml:space="preserve">C16H12O4</t>
+  </si>
+  <si>
     <t xml:space="preserve">5280378</t>
   </si>
   <si>
     <t xml:space="preserve">calycosin</t>
   </si>
   <si>
+    <t xml:space="preserve">C16H12O5</t>
+  </si>
+  <si>
     <t xml:space="preserve">5280448</t>
   </si>
   <si>
     <t xml:space="preserve">hydroxylation + glucuronide conjugation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H20O11</t>
+  </si>
+  <si>
     <t xml:space="preserve">glucuronide conjugation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C21H21O9</t>
+  </si>
+  <si>
     <t xml:space="preserve">decarboxylation + glucuronidation of unknown</t>
   </si>
   <si>
+    <t xml:space="preserve">C21H20O10</t>
+  </si>
+  <si>
     <t xml:space="preserve">ononin</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H22O9</t>
+  </si>
+  <si>
     <t xml:space="preserve">442813</t>
   </si>
   <si>
     <t xml:space="preserve">methylnissolin</t>
   </si>
   <si>
+    <t xml:space="preserve">C17H16O5</t>
+  </si>
+  <si>
     <t xml:space="preserve">5319733</t>
   </si>
   <si>
     <t xml:space="preserve">calycosin 7-o-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H22O10</t>
+  </si>
+  <si>
     <t xml:space="preserve">5318267</t>
   </si>
   <si>
     <t xml:space="preserve">astragaloside iv</t>
   </si>
   <si>
+    <t xml:space="preserve">C41H68O14</t>
+  </si>
+  <si>
     <t xml:space="preserve">13943297</t>
   </si>
   <si>
     <t xml:space="preserve">9,10-dimethoxypterocarpan-3-o-beta-d-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">C23H26O10</t>
+  </si>
+  <si>
     <t xml:space="preserve">86566448</t>
   </si>
   <si>
     <t xml:space="preserve">(r)-isomucronulatol</t>
   </si>
   <si>
+    <t xml:space="preserve">C17H18O5</t>
+  </si>
+  <si>
     <t xml:space="preserve">10380176</t>
   </si>
   <si>
     <t xml:space="preserve">astragaloside ii</t>
   </si>
   <si>
+    <t xml:space="preserve">C43H70O15</t>
+  </si>
+  <si>
     <t xml:space="preserve">13996693</t>
   </si>
   <si>
     <t xml:space="preserve">formononetin 7-o-glucuronide</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H20O10</t>
+  </si>
+  <si>
     <t xml:space="preserve">71316927</t>
   </si>
   <si>
     <t xml:space="preserve">daidzein-7-o-glucuronide</t>
   </si>
   <si>
+    <t xml:space="preserve">C21H18O10</t>
+  </si>
+  <si>
     <t xml:space="preserve">11316354</t>
   </si>
   <si>
     <t xml:space="preserve">calycosin-7-β-glucoside-3'-glucuronide</t>
   </si>
   <si>
+    <t xml:space="preserve">C28H30O16</t>
+  </si>
+  <si>
     <t xml:space="preserve">calycosin-3'-o-glucuronide</t>
   </si>
   <si>
     <t xml:space="preserve">tyrosine</t>
   </si>
   <si>
+    <t xml:space="preserve">C9H11NO3</t>
+  </si>
+  <si>
     <t xml:space="preserve">6057</t>
   </si>
   <si>
     <t xml:space="preserve">tryptophan</t>
   </si>
   <si>
+    <t xml:space="preserve">C11H12N2O2</t>
+  </si>
+  <si>
     <t xml:space="preserve">6305</t>
   </si>
   <si>
     <t xml:space="preserve">syringin</t>
   </si>
   <si>
+    <t xml:space="preserve">C17H24O9</t>
+  </si>
+  <si>
     <t xml:space="preserve">5316860</t>
   </si>
   <si>
     <t xml:space="preserve">syringic acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C9H10O5</t>
+  </si>
+  <si>
     <t xml:space="preserve">10742</t>
   </si>
   <si>
     <t xml:space="preserve">syringaldehyde</t>
   </si>
   <si>
+    <t xml:space="preserve">C9H10O4</t>
+  </si>
+  <si>
     <t xml:space="preserve">8655</t>
   </si>
   <si>
     <t xml:space="preserve">soyasaponin i</t>
   </si>
   <si>
+    <t xml:space="preserve">C48H78O18</t>
+  </si>
+  <si>
     <t xml:space="preserve">122097</t>
   </si>
   <si>
     <t xml:space="preserve">sinapic acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C11H12O5</t>
+  </si>
+  <si>
     <t xml:space="preserve">637775</t>
   </si>
   <si>
     <t xml:space="preserve">rhamnocitrin 3,4'-diglucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">C28H32O16</t>
+  </si>
+  <si>
     <t xml:space="preserve">44259548</t>
   </si>
   <si>
     <t xml:space="preserve">raffinose</t>
   </si>
   <si>
+    <t xml:space="preserve">C18H32O16</t>
+  </si>
+  <si>
     <t xml:space="preserve">439242</t>
   </si>
   <si>
     <t xml:space="preserve">pratensein 7-o-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H22O11</t>
+  </si>
+  <si>
     <t xml:space="preserve">44257307</t>
   </si>
   <si>
     <t xml:space="preserve">phenylalanine</t>
   </si>
   <si>
+    <t xml:space="preserve">C9H11NO2</t>
+  </si>
+  <si>
     <t xml:space="preserve">6140</t>
   </si>
   <si>
     <t xml:space="preserve">nicotinic acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C6H5NO2</t>
+  </si>
+  <si>
     <t xml:space="preserve">938</t>
   </si>
   <si>
     <t xml:space="preserve">markhamioside f</t>
   </si>
   <si>
+    <t xml:space="preserve">C19H26O13</t>
+  </si>
+  <si>
     <t xml:space="preserve">101182651</t>
   </si>
   <si>
     <t xml:space="preserve">leucine</t>
   </si>
   <si>
+    <t xml:space="preserve">C6H13NO2</t>
+  </si>
+  <si>
     <t xml:space="preserve">6106</t>
   </si>
   <si>
     <t xml:space="preserve">isomucronulatol-2',5'-di-o-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">C29H38O16</t>
+  </si>
+  <si>
     <t xml:space="preserve">isomucronulatol 7-o-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">C23H28O10</t>
+  </si>
+  <si>
     <t xml:space="preserve">125142</t>
   </si>
   <si>
     <t xml:space="preserve">isomucronulatol 7,2'-di-o-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">C29H38O15</t>
+  </si>
+  <si>
     <t xml:space="preserve">15689653</t>
   </si>
   <si>
     <t xml:space="preserve">isoferulic acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C10H10O4</t>
+  </si>
+  <si>
     <t xml:space="preserve">736186</t>
   </si>
   <si>
     <t xml:space="preserve">isoastragaloside i</t>
   </si>
   <si>
+    <t xml:space="preserve">C45H72O16</t>
+  </si>
+  <si>
     <t xml:space="preserve">60148697</t>
   </si>
   <si>
     <t xml:space="preserve">hexose</t>
   </si>
   <si>
+    <t xml:space="preserve">C6H12O6</t>
+  </si>
+  <si>
     <t xml:space="preserve">206</t>
   </si>
   <si>
     <t xml:space="preserve">gamma-aminobutyric acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C4H9NO2</t>
+  </si>
+  <si>
     <t xml:space="preserve">119</t>
   </si>
   <si>
@@ -497,9 +719,15 @@
     <t xml:space="preserve">emodin-di-o-glucoside</t>
   </si>
   <si>
+    <t xml:space="preserve">C27H30O15</t>
+  </si>
+  <si>
     <t xml:space="preserve">2-(hydroxymethyl)-6-[[3,4,5-trihydroxy-5-(hydroxymethyl)oxolan-2-yl]methoxy]oxane-3,4,5-triol</t>
   </si>
   <si>
+    <t xml:space="preserve">C12H22O11</t>
+  </si>
+  <si>
     <t xml:space="preserve">3749604</t>
   </si>
   <si>
@@ -512,36 +740,54 @@
     <t xml:space="preserve">nona-2,4-dienoic acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C9H14O2</t>
+  </si>
+  <si>
     <t xml:space="preserve">54498674</t>
   </si>
   <si>
     <t xml:space="preserve">choline</t>
   </si>
   <si>
+    <t xml:space="preserve">C5H14NO+</t>
+  </si>
+  <si>
     <t xml:space="preserve">305</t>
   </si>
   <si>
     <t xml:space="preserve">caffeic acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C9H8O4</t>
+  </si>
+  <si>
     <t xml:space="preserve">689043</t>
   </si>
   <si>
     <t xml:space="preserve">azelaic acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C9H16O4</t>
+  </si>
+  <si>
     <t xml:space="preserve">2266</t>
   </si>
   <si>
     <t xml:space="preserve">wistariasaponin c</t>
   </si>
   <si>
+    <t xml:space="preserve">C47H76O17</t>
+  </si>
+  <si>
     <t xml:space="preserve">21634074</t>
   </si>
   <si>
     <t xml:space="preserve">astragaloside vii</t>
   </si>
   <si>
+    <t xml:space="preserve">C47H78O19</t>
+  </si>
+  <si>
     <t xml:space="preserve">14241100</t>
   </si>
   <si>
@@ -572,48 +818,78 @@
     <t xml:space="preserve">asparagine</t>
   </si>
   <si>
+    <t xml:space="preserve">C4H8N2O3</t>
+  </si>
+  <si>
     <t xml:space="preserve">6267</t>
   </si>
   <si>
     <t xml:space="preserve">adenosine</t>
   </si>
   <si>
+    <t xml:space="preserve">C10H13N5O4</t>
+  </si>
+  <si>
     <t xml:space="preserve">60961</t>
   </si>
   <si>
     <t xml:space="preserve">acetyl astragaloside i</t>
   </si>
   <si>
+    <t xml:space="preserve">C47H74O17</t>
+  </si>
+  <si>
     <t xml:space="preserve">6''-o-acetylononin</t>
   </si>
   <si>
+    <t xml:space="preserve">C24H24O10</t>
+  </si>
+  <si>
     <t xml:space="preserve">102463148</t>
   </si>
   <si>
     <t xml:space="preserve">3,4-dihydroxybenzoic acid</t>
   </si>
   <si>
+    <t xml:space="preserve">C7H6O4</t>
+  </si>
+  <si>
     <t xml:space="preserve">72</t>
   </si>
   <si>
     <t xml:space="preserve">cyclocanthoside e</t>
   </si>
   <si>
+    <t xml:space="preserve">C41H70O14</t>
+  </si>
+  <si>
     <t xml:space="preserve">21633193</t>
   </si>
   <si>
     <t xml:space="preserve">sulfated isomucronulatol</t>
   </si>
   <si>
+    <t xml:space="preserve">C17H18O8S</t>
+  </si>
+  <si>
     <t xml:space="preserve">sulfated formononetin</t>
   </si>
   <si>
+    <t xml:space="preserve">C16H12O7S</t>
+  </si>
+  <si>
     <t xml:space="preserve">sulfated calycosin</t>
   </si>
   <si>
+    <t xml:space="preserve">C16H12O8S</t>
+  </si>
+  <si>
     <t xml:space="preserve">rhamnocitrin</t>
   </si>
   <si>
+    <t xml:space="preserve">C16H12O6</t>
+  </si>
+  <si>
     <t xml:space="preserve">5320946</t>
   </si>
   <si>
@@ -626,9 +902,15 @@
     <t xml:space="preserve">glucuronidated rhamnocitrin</t>
   </si>
   <si>
+    <t xml:space="preserve">C22H20O12</t>
+  </si>
+  <si>
     <t xml:space="preserve">glucuronidated isomucronulatol</t>
   </si>
   <si>
+    <t xml:space="preserve">C23H26O11</t>
+  </si>
+  <si>
     <t xml:space="preserve">formononetin 7-glucuronide</t>
   </si>
   <si>
@@ -641,18 +923,27 @@
     <t xml:space="preserve">betaine</t>
   </si>
   <si>
+    <t xml:space="preserve">C5H11NO2</t>
+  </si>
+  <si>
     <t xml:space="preserve">247</t>
   </si>
   <si>
     <t xml:space="preserve">5-hydroxy-7,8-dimethoxyflavanone + glucuronide conjugation</t>
   </si>
   <si>
+    <t xml:space="preserve">C23H24O11</t>
+  </si>
+  <si>
     <t xml:space="preserve">isomer of 3-hydro-9, 10-dimethoxypterocarpan</t>
   </si>
   <si>
     <t xml:space="preserve">daidzein</t>
   </si>
   <si>
+    <t xml:space="preserve">C15H10O4</t>
+  </si>
+  <si>
     <t xml:space="preserve">5281708</t>
   </si>
   <si>
@@ -665,6 +956,9 @@
     <t xml:space="preserve">glucuronic acid conjugate of demethylcalycosin</t>
   </si>
   <si>
+    <t xml:space="preserve">C21H18O11</t>
+  </si>
+  <si>
     <t xml:space="preserve">glucuronic acid conjugate of daidzein</t>
   </si>
   <si>
@@ -677,12 +971,18 @@
     <t xml:space="preserve">kaempferitrin</t>
   </si>
   <si>
+    <t xml:space="preserve">C27H30O14</t>
+  </si>
+  <si>
     <t xml:space="preserve">5486199</t>
   </si>
   <si>
     <t xml:space="preserve">astragaloside-ii</t>
   </si>
   <si>
+    <t xml:space="preserve">C41H66O15</t>
+  </si>
+  <si>
     <t xml:space="preserve">71306915</t>
   </si>
   <si>
@@ -704,60 +1004,42 @@
     <t xml:space="preserve">5318767</t>
   </si>
   <si>
+    <t xml:space="preserve">aconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tan-2012-in vivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tan-2012-in vivo; Zhang-2024-in vivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hypaconine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24H39NO8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76189740</t>
+  </si>
+  <si>
     <t xml:space="preserve">karakolidine</t>
   </si>
   <si>
-    <t xml:space="preserve">C22H35NO5</t>
-  </si>
-  <si>
     <t xml:space="preserve">177825366</t>
   </si>
   <si>
-    <t xml:space="preserve">Tan.2012</t>
-  </si>
-  <si>
     <t xml:space="preserve">chuanfumine</t>
   </si>
   <si>
     <t xml:space="preserve">177827759</t>
   </si>
   <si>
-    <t xml:space="preserve">mesaconine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H39NO9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aconine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25H41NO9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C22H31NO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hypaconine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H39NO8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76189740</t>
-  </si>
-  <si>
     <t xml:space="preserve">fuziline</t>
   </si>
   <si>
-    <t xml:space="preserve">C24H39NO7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H39NO6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24H39NO5</t>
-  </si>
-  <si>
     <t xml:space="preserve">14-acetylkarakoline</t>
   </si>
   <si>
@@ -767,142 +1049,79 @@
     <t xml:space="preserve">177825823</t>
   </si>
   <si>
-    <t xml:space="preserve">C31H43NO10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C32H45NO10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15559774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C31H43NO9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78358535</t>
+    <t xml:space="preserve">calycosin-7-O-β-D-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin-7-O-β-D-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6aR,11aR)-9,10-dimethoxypterocarpan-3-O-β-D-glucoside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11968435</t>
   </si>
   <si>
     <t xml:space="preserve">2'-hydroxy-3',4'-dimethoxyisoflavan-7-O-β-D-glucoside</t>
   </si>
   <si>
-    <t xml:space="preserve">C₂₃H₂₈O₁₀</t>
+    <t xml:space="preserve">15689656</t>
   </si>
   <si>
     <t xml:space="preserve">astragaloside IV</t>
   </si>
   <si>
-    <t xml:space="preserve">C41H68O14</t>
-  </si>
-  <si>
     <t xml:space="preserve">45006101</t>
   </si>
   <si>
     <t xml:space="preserve">astragaloside II</t>
   </si>
   <si>
-    <t xml:space="preserve">C43H70O15</t>
-  </si>
-  <si>
     <t xml:space="preserve">soyasaponin I</t>
   </si>
   <si>
-    <t xml:space="preserve">C48H78O18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16H12O5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16H12O4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calycosin 7-O-β-D-glucoside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C22H22O10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">formononetin-O-β-D-glucoside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C22H22O9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,10-dimethoxy-pterocarpan-3-O-β-D-glucoside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C23H28O10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11968435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhang.2024</t>
+    <t xml:space="preserve">chasmanine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhang-2024-in vivo</t>
   </si>
   <si>
     <t xml:space="preserve">senbusine B</t>
   </si>
   <si>
-    <t xml:space="preserve">C23H37NO5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11452543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chasmanine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25H41NO6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16-β-Hydroxycardiopetaline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C23H37NO6</t>
-  </si>
-  <si>
     <t xml:space="preserve">158049</t>
   </si>
   <si>
     <t xml:space="preserve">14-acetyltalatizamine</t>
   </si>
   <si>
-    <t xml:space="preserve">Demethyl neoline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demethyl isotalatizidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demethyl dehydrogen isotalatizidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dehydration karakoline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demethyl dehydrogen neoline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dehydration isotalatizidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demethyl karakolidine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formononetin-O-glucuronide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C22H20O10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calycosin-O-glucuronide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C22H20O11</t>
+    <t xml:space="preserve">13343318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16β-hydroxycardiopetaline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21H33NO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102511299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calycosin-7-O-β-D-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H20NO11</t>
   </si>
   <si>
     <t xml:space="preserve">101396032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formononetin 7-O-β-D-glucuronide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22H20NO10</t>
   </si>
 </sst>
 </file>
@@ -1250,3375 +1469,3498 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2"/>
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3"/>
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
+      <c r="G3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="n">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4"/>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
+      <c r="G4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5"/>
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
       <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6"/>
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
       <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7"/>
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
       <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
+        <v>28</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8"/>
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
       <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9"/>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
+      <c r="G9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10"/>
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
       <c r="E10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
+        <v>38</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11"/>
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
       <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12"/>
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
       <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13"/>
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
       <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
+        <v>47</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14"/>
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
       <c r="E14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15"/>
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
       <c r="E15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
+        <v>51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" t="n">
         <v>6</v>
       </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16"/>
-      <c r="E16" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
+      <c r="G16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" t="n">
         <v>6</v>
       </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17"/>
-      <c r="E17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
+      <c r="G17" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18"/>
+        <v>58</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
       <c r="E18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" t="s">
-        <v>10</v>
+        <v>59</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19"/>
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
       <c r="E19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" t="n">
         <v>6</v>
       </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20"/>
-      <c r="E20" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
+      <c r="G20" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21"/>
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
+        <v>65</v>
+      </c>
       <c r="E21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
         <v>44</v>
       </c>
-      <c r="D22"/>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23"/>
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
       <c r="E23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24"/>
+        <v>69</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
       <c r="E24" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25"/>
+        <v>70</v>
+      </c>
+      <c r="D25" t="s">
+        <v>71</v>
+      </c>
       <c r="E25" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26"/>
+        <v>72</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
       <c r="E26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27"/>
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
+        <v>75</v>
+      </c>
       <c r="E27" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" t="s">
+        <v>44</v>
+      </c>
+      <c r="F28" t="n">
         <v>6</v>
       </c>
-      <c r="B28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28"/>
-      <c r="E28" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" t="s">
-        <v>10</v>
+      <c r="G28" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29"/>
+        <v>78</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
       <c r="E29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30"/>
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
       <c r="E30" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" t="s">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31"/>
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>34</v>
+      </c>
       <c r="E31" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" t="s">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" t="s">
-        <v>52</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C32"/>
       <c r="D32"/>
-      <c r="E32" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" t="s">
-        <v>10</v>
+      <c r="E32"/>
+      <c r="F32" t="n">
+        <v>26</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33"/>
+        <v>83</v>
+      </c>
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
       <c r="E33" t="s">
-        <v>30</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
+        <v>85</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34"/>
+        <v>86</v>
+      </c>
+      <c r="D34" t="s">
+        <v>87</v>
+      </c>
       <c r="E34" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" t="s">
-        <v>10</v>
+        <v>88</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35"/>
+        <v>89</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
       <c r="E35" t="s">
-        <v>55</v>
-      </c>
-      <c r="F35" t="s">
-        <v>10</v>
+        <v>90</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36"/>
+        <v>91</v>
+      </c>
+      <c r="D36" t="s">
+        <v>92</v>
+      </c>
       <c r="E36" t="s">
-        <v>57</v>
-      </c>
-      <c r="F36" t="s">
-        <v>10</v>
+        <v>93</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37"/>
+        <v>94</v>
+      </c>
+      <c r="D37" t="s">
+        <v>92</v>
+      </c>
       <c r="E37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D38"/>
+        <v>95</v>
+      </c>
+      <c r="D38" t="s">
+        <v>49</v>
+      </c>
       <c r="E38" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39"/>
+        <v>96</v>
+      </c>
+      <c r="D39" t="s">
+        <v>97</v>
+      </c>
       <c r="E39" t="s">
-        <v>63</v>
-      </c>
-      <c r="F39" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40"/>
+        <v>98</v>
+      </c>
+      <c r="D40" t="s">
+        <v>99</v>
+      </c>
       <c r="E40" t="s">
-        <v>65</v>
-      </c>
-      <c r="F40" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
-      </c>
-      <c r="D41"/>
+        <v>100</v>
+      </c>
+      <c r="D41" t="s">
+        <v>101</v>
+      </c>
       <c r="E41" t="s">
-        <v>30</v>
-      </c>
-      <c r="F41" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42"/>
+        <v>102</v>
+      </c>
+      <c r="D42" t="s">
+        <v>92</v>
+      </c>
       <c r="E42" t="s">
-        <v>30</v>
-      </c>
-      <c r="F42" t="s">
-        <v>10</v>
+        <v>103</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43"/>
+        <v>104</v>
+      </c>
+      <c r="D43" t="s">
+        <v>105</v>
+      </c>
       <c r="E43" t="s">
-        <v>30</v>
-      </c>
-      <c r="F43" t="s">
-        <v>10</v>
+        <v>106</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
-      </c>
-      <c r="D44"/>
+        <v>107</v>
+      </c>
+      <c r="D44" t="s">
+        <v>108</v>
+      </c>
       <c r="E44" t="s">
-        <v>30</v>
-      </c>
-      <c r="F44" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45"/>
+        <v>109</v>
+      </c>
+      <c r="D45" t="s">
+        <v>110</v>
+      </c>
       <c r="E45" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46"/>
+        <v>111</v>
+      </c>
+      <c r="D46" t="s">
+        <v>92</v>
+      </c>
       <c r="E46" t="s">
-        <v>72</v>
-      </c>
-      <c r="F46" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>73</v>
-      </c>
-      <c r="D47"/>
+        <v>112</v>
+      </c>
+      <c r="D47" t="s">
+        <v>113</v>
+      </c>
       <c r="E47" t="s">
-        <v>74</v>
-      </c>
-      <c r="F47" t="s">
-        <v>10</v>
+        <v>114</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48"/>
+        <v>115</v>
+      </c>
+      <c r="D48" t="s">
+        <v>34</v>
+      </c>
       <c r="E48" t="s">
-        <v>30</v>
-      </c>
-      <c r="F48" t="s">
-        <v>10</v>
+        <v>116</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49"/>
+        <v>117</v>
+      </c>
+      <c r="D49" t="s">
+        <v>118</v>
+      </c>
       <c r="E49" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" t="s">
-        <v>10</v>
+        <v>119</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50"/>
+        <v>120</v>
+      </c>
+      <c r="D50" t="s">
+        <v>34</v>
+      </c>
       <c r="E50" t="s">
-        <v>30</v>
-      </c>
-      <c r="F50" t="s">
-        <v>10</v>
+        <v>121</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D51"/>
+        <v>122</v>
+      </c>
+      <c r="D51" t="s">
+        <v>123</v>
+      </c>
       <c r="E51" t="s">
-        <v>79</v>
-      </c>
-      <c r="F51" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52"/>
+        <v>124</v>
+      </c>
+      <c r="D52" t="s">
+        <v>125</v>
+      </c>
       <c r="E52" t="s">
-        <v>81</v>
-      </c>
-      <c r="F52" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C53" t="s">
-        <v>82</v>
-      </c>
-      <c r="D53"/>
+        <v>128</v>
+      </c>
+      <c r="D53" t="s">
+        <v>129</v>
+      </c>
       <c r="E53" t="s">
-        <v>83</v>
-      </c>
-      <c r="F53" t="s">
-        <v>10</v>
+        <v>130</v>
+      </c>
+      <c r="F53" t="n">
+        <v>16</v>
+      </c>
+      <c r="G53" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
-      </c>
-      <c r="D54"/>
+        <v>131</v>
+      </c>
+      <c r="D54" t="s">
+        <v>132</v>
+      </c>
       <c r="E54" t="s">
-        <v>85</v>
-      </c>
-      <c r="F54" t="s">
-        <v>10</v>
+        <v>133</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12</v>
+      </c>
+      <c r="G54" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
-        <v>86</v>
-      </c>
-      <c r="D55"/>
+        <v>134</v>
+      </c>
+      <c r="D55" t="s">
+        <v>135</v>
+      </c>
       <c r="E55" t="s">
-        <v>30</v>
-      </c>
-      <c r="F55" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C56" t="s">
-        <v>87</v>
-      </c>
-      <c r="D56"/>
+        <v>136</v>
+      </c>
+      <c r="D56" t="s">
+        <v>137</v>
+      </c>
       <c r="E56" t="s">
-        <v>30</v>
-      </c>
-      <c r="F56" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B57" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
-        <v>90</v>
-      </c>
-      <c r="D57"/>
+        <v>138</v>
+      </c>
+      <c r="D57" t="s">
+        <v>139</v>
+      </c>
       <c r="E57" t="s">
-        <v>91</v>
-      </c>
-      <c r="F57" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58"/>
+        <v>140</v>
+      </c>
+      <c r="D58" t="s">
+        <v>141</v>
+      </c>
       <c r="E58" t="s">
-        <v>93</v>
-      </c>
-      <c r="F58" t="s">
-        <v>10</v>
+        <v>142</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>42</v>
-      </c>
-      <c r="D59"/>
+        <v>143</v>
+      </c>
+      <c r="D59" t="s">
+        <v>144</v>
+      </c>
       <c r="E59" t="s">
-        <v>30</v>
-      </c>
-      <c r="F59" t="s">
-        <v>10</v>
+        <v>145</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>43</v>
-      </c>
-      <c r="D60"/>
+        <v>146</v>
+      </c>
+      <c r="D60" t="s">
+        <v>147</v>
+      </c>
       <c r="E60" t="s">
-        <v>30</v>
-      </c>
-      <c r="F60" t="s">
-        <v>10</v>
+        <v>148</v>
+      </c>
+      <c r="F60" t="n">
+        <v>12</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B61" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
-      </c>
-      <c r="D61"/>
+        <v>149</v>
+      </c>
+      <c r="D61" t="s">
+        <v>150</v>
+      </c>
       <c r="E61" t="s">
-        <v>30</v>
-      </c>
-      <c r="F61" t="s">
-        <v>10</v>
+        <v>151</v>
+      </c>
+      <c r="F61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
-      </c>
-      <c r="D62"/>
+        <v>152</v>
+      </c>
+      <c r="D62" t="s">
+        <v>153</v>
+      </c>
       <c r="E62" t="s">
-        <v>30</v>
-      </c>
-      <c r="F62" t="s">
-        <v>10</v>
+        <v>154</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
-      </c>
-      <c r="D63"/>
+        <v>155</v>
+      </c>
+      <c r="D63" t="s">
+        <v>156</v>
+      </c>
       <c r="E63" t="s">
-        <v>30</v>
-      </c>
-      <c r="F63" t="s">
-        <v>10</v>
+        <v>157</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
-      </c>
-      <c r="D64"/>
+        <v>158</v>
+      </c>
+      <c r="D64" t="s">
+        <v>159</v>
+      </c>
       <c r="E64" t="s">
-        <v>98</v>
-      </c>
-      <c r="F64" t="s">
-        <v>10</v>
+        <v>160</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s">
-        <v>99</v>
-      </c>
-      <c r="D65"/>
+        <v>161</v>
+      </c>
+      <c r="D65" t="s">
+        <v>162</v>
+      </c>
       <c r="E65" t="s">
-        <v>100</v>
-      </c>
-      <c r="F65" t="s">
-        <v>10</v>
+        <v>163</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C66" t="s">
-        <v>101</v>
-      </c>
-      <c r="D66"/>
+        <v>164</v>
+      </c>
+      <c r="D66" t="s">
+        <v>165</v>
+      </c>
       <c r="E66" t="s">
-        <v>102</v>
-      </c>
-      <c r="F66" t="s">
-        <v>10</v>
+        <v>166</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
-      </c>
-      <c r="D67"/>
+        <v>167</v>
+      </c>
+      <c r="D67" t="s">
+        <v>168</v>
+      </c>
       <c r="E67" t="s">
-        <v>104</v>
-      </c>
-      <c r="F67" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
-      </c>
-      <c r="D68"/>
+        <v>169</v>
+      </c>
+      <c r="D68" t="s">
+        <v>135</v>
+      </c>
       <c r="E68" t="s">
-        <v>106</v>
-      </c>
-      <c r="F68" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B69" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
-      </c>
-      <c r="D69"/>
+        <v>170</v>
+      </c>
+      <c r="D69" t="s">
+        <v>171</v>
+      </c>
       <c r="E69" t="s">
-        <v>108</v>
-      </c>
-      <c r="F69" t="s">
-        <v>10</v>
+        <v>172</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C70" t="s">
-        <v>109</v>
-      </c>
-      <c r="D70"/>
+        <v>173</v>
+      </c>
+      <c r="D70" t="s">
+        <v>174</v>
+      </c>
       <c r="E70" t="s">
-        <v>110</v>
-      </c>
-      <c r="F70" t="s">
-        <v>10</v>
+        <v>175</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C71" t="s">
-        <v>111</v>
-      </c>
-      <c r="D71"/>
+        <v>176</v>
+      </c>
+      <c r="D71" t="s">
+        <v>177</v>
+      </c>
       <c r="E71" t="s">
-        <v>112</v>
-      </c>
-      <c r="F71" t="s">
-        <v>10</v>
+        <v>178</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C72" t="s">
-        <v>113</v>
-      </c>
-      <c r="D72"/>
+        <v>179</v>
+      </c>
+      <c r="D72" t="s">
+        <v>180</v>
+      </c>
       <c r="E72" t="s">
-        <v>114</v>
-      </c>
-      <c r="F72" t="s">
-        <v>10</v>
+        <v>181</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
-      </c>
-      <c r="D73"/>
+        <v>182</v>
+      </c>
+      <c r="D73" t="s">
+        <v>183</v>
+      </c>
       <c r="E73" t="s">
-        <v>30</v>
-      </c>
-      <c r="F73" t="s">
-        <v>10</v>
+        <v>184</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>116</v>
-      </c>
-      <c r="D74"/>
+        <v>185</v>
+      </c>
+      <c r="D74" t="s">
+        <v>186</v>
+      </c>
       <c r="E74" t="s">
-        <v>30</v>
-      </c>
-      <c r="F74" t="s">
-        <v>10</v>
+        <v>187</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C75" t="s">
-        <v>117</v>
-      </c>
-      <c r="D75"/>
+        <v>188</v>
+      </c>
+      <c r="D75" t="s">
+        <v>189</v>
+      </c>
       <c r="E75" t="s">
-        <v>118</v>
-      </c>
-      <c r="F75" t="s">
-        <v>10</v>
+        <v>190</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C76" t="s">
-        <v>119</v>
-      </c>
-      <c r="D76"/>
+        <v>191</v>
+      </c>
+      <c r="D76" t="s">
+        <v>192</v>
+      </c>
       <c r="E76" t="s">
-        <v>120</v>
-      </c>
-      <c r="F76" t="s">
-        <v>10</v>
+        <v>193</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C77" t="s">
-        <v>121</v>
-      </c>
-      <c r="D77"/>
+        <v>194</v>
+      </c>
+      <c r="D77" t="s">
+        <v>195</v>
+      </c>
       <c r="E77" t="s">
-        <v>122</v>
-      </c>
-      <c r="F77" t="s">
-        <v>10</v>
+        <v>196</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B78" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C78" t="s">
-        <v>123</v>
-      </c>
-      <c r="D78"/>
+        <v>197</v>
+      </c>
+      <c r="D78" t="s">
+        <v>198</v>
+      </c>
       <c r="E78" t="s">
-        <v>124</v>
-      </c>
-      <c r="F78" t="s">
-        <v>10</v>
+        <v>199</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
-      </c>
-      <c r="D79"/>
+        <v>200</v>
+      </c>
+      <c r="D79" t="s">
+        <v>201</v>
+      </c>
       <c r="E79" t="s">
-        <v>126</v>
-      </c>
-      <c r="F79" t="s">
-        <v>10</v>
+        <v>202</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C80" t="s">
-        <v>127</v>
-      </c>
-      <c r="D80"/>
+        <v>203</v>
+      </c>
+      <c r="D80" t="s">
+        <v>204</v>
+      </c>
       <c r="E80" t="s">
-        <v>128</v>
-      </c>
-      <c r="F80" t="s">
-        <v>10</v>
+        <v>205</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C81" t="s">
-        <v>129</v>
-      </c>
-      <c r="D81"/>
+        <v>206</v>
+      </c>
+      <c r="D81" t="s">
+        <v>207</v>
+      </c>
       <c r="E81" t="s">
-        <v>130</v>
-      </c>
-      <c r="F81" t="s">
-        <v>10</v>
+        <v>208</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
-      </c>
-      <c r="D82"/>
+        <v>209</v>
+      </c>
+      <c r="D82" t="s">
+        <v>210</v>
+      </c>
       <c r="E82" t="s">
-        <v>132</v>
-      </c>
-      <c r="F82" t="s">
-        <v>10</v>
+        <v>211</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D83"/>
+        <v>212</v>
+      </c>
+      <c r="D83" t="s">
+        <v>213</v>
+      </c>
       <c r="E83" t="s">
-        <v>134</v>
-      </c>
-      <c r="F83" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C84" t="s">
-        <v>135</v>
-      </c>
-      <c r="D84"/>
+        <v>214</v>
+      </c>
+      <c r="D84" t="s">
+        <v>215</v>
+      </c>
       <c r="E84" t="s">
-        <v>136</v>
-      </c>
-      <c r="F84" t="s">
-        <v>10</v>
+        <v>216</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C85" t="s">
-        <v>137</v>
-      </c>
-      <c r="D85"/>
+        <v>217</v>
+      </c>
+      <c r="D85" t="s">
+        <v>218</v>
+      </c>
       <c r="E85" t="s">
-        <v>138</v>
-      </c>
-      <c r="F85" t="s">
-        <v>10</v>
+        <v>219</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B86" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C86" t="s">
-        <v>139</v>
-      </c>
-      <c r="D86"/>
+        <v>220</v>
+      </c>
+      <c r="D86" t="s">
+        <v>221</v>
+      </c>
       <c r="E86" t="s">
-        <v>140</v>
-      </c>
-      <c r="F86" t="s">
-        <v>10</v>
+        <v>222</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B87" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C87" t="s">
-        <v>141</v>
-      </c>
-      <c r="D87"/>
+        <v>223</v>
+      </c>
+      <c r="D87" t="s">
+        <v>224</v>
+      </c>
       <c r="E87" t="s">
-        <v>142</v>
-      </c>
-      <c r="F87" t="s">
-        <v>10</v>
+        <v>225</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C88" t="s">
-        <v>143</v>
-      </c>
-      <c r="D88"/>
+        <v>226</v>
+      </c>
+      <c r="D88" t="s">
+        <v>227</v>
+      </c>
       <c r="E88" t="s">
-        <v>144</v>
-      </c>
-      <c r="F88" t="s">
-        <v>10</v>
+        <v>228</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C89" t="s">
-        <v>145</v>
-      </c>
-      <c r="D89"/>
+        <v>229</v>
+      </c>
+      <c r="D89" t="s">
+        <v>230</v>
+      </c>
       <c r="E89" t="s">
-        <v>30</v>
-      </c>
-      <c r="F89" t="s">
-        <v>10</v>
+        <v>231</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
-      </c>
-      <c r="D90"/>
+        <v>232</v>
+      </c>
+      <c r="D90" t="s">
+        <v>221</v>
+      </c>
       <c r="E90" t="s">
-        <v>147</v>
-      </c>
-      <c r="F90" t="s">
-        <v>10</v>
+        <v>233</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C91" t="s">
-        <v>148</v>
-      </c>
-      <c r="D91"/>
+        <v>234</v>
+      </c>
+      <c r="D91" t="s">
+        <v>235</v>
+      </c>
       <c r="E91" t="s">
-        <v>149</v>
-      </c>
-      <c r="F91" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>150</v>
-      </c>
-      <c r="D92"/>
+        <v>236</v>
+      </c>
+      <c r="D92" t="s">
+        <v>237</v>
+      </c>
       <c r="E92" t="s">
-        <v>151</v>
-      </c>
-      <c r="F92" t="s">
-        <v>10</v>
+        <v>238</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B93" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
-      </c>
-      <c r="D93"/>
+        <v>239</v>
+      </c>
+      <c r="D93" t="s">
+        <v>139</v>
+      </c>
       <c r="E93" t="s">
-        <v>153</v>
-      </c>
-      <c r="F93" t="s">
-        <v>10</v>
+        <v>240</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B94" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C94" t="s">
-        <v>154</v>
-      </c>
-      <c r="D94"/>
+        <v>241</v>
+      </c>
+      <c r="D94" t="s">
+        <v>242</v>
+      </c>
       <c r="E94" t="s">
-        <v>155</v>
-      </c>
-      <c r="F94" t="s">
-        <v>10</v>
+        <v>243</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B95" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>156</v>
-      </c>
-      <c r="D95"/>
+        <v>244</v>
+      </c>
+      <c r="D95" t="s">
+        <v>245</v>
+      </c>
       <c r="E95" t="s">
-        <v>157</v>
-      </c>
-      <c r="F95" t="s">
-        <v>10</v>
+        <v>246</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B96" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>158</v>
-      </c>
-      <c r="D96"/>
+        <v>247</v>
+      </c>
+      <c r="D96" t="s">
+        <v>248</v>
+      </c>
       <c r="E96" t="s">
-        <v>159</v>
-      </c>
-      <c r="F96" t="s">
-        <v>10</v>
+        <v>249</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B97" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>160</v>
-      </c>
-      <c r="D97"/>
+        <v>250</v>
+      </c>
+      <c r="D97" t="s">
+        <v>251</v>
+      </c>
       <c r="E97" t="s">
-        <v>30</v>
-      </c>
-      <c r="F97" t="s">
-        <v>10</v>
+        <v>252</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B98" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C98" t="s">
-        <v>161</v>
-      </c>
-      <c r="D98"/>
+        <v>253</v>
+      </c>
+      <c r="D98" t="s">
+        <v>254</v>
+      </c>
       <c r="E98" t="s">
-        <v>162</v>
-      </c>
-      <c r="F98" t="s">
-        <v>10</v>
+        <v>255</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B99" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C99" t="s">
-        <v>163</v>
-      </c>
-      <c r="D99"/>
+        <v>256</v>
+      </c>
+      <c r="D99" t="s">
+        <v>257</v>
+      </c>
       <c r="E99" t="s">
-        <v>164</v>
-      </c>
-      <c r="F99" t="s">
-        <v>10</v>
+        <v>258</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B100" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C100" t="s">
-        <v>165</v>
-      </c>
-      <c r="D100"/>
+        <v>259</v>
+      </c>
+      <c r="D100" t="s">
+        <v>257</v>
+      </c>
       <c r="E100" t="s">
-        <v>166</v>
-      </c>
-      <c r="F100" t="s">
-        <v>10</v>
+        <v>260</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B101" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C101" t="s">
-        <v>167</v>
-      </c>
-      <c r="D101"/>
+        <v>261</v>
+      </c>
+      <c r="D101" t="s">
+        <v>257</v>
+      </c>
       <c r="E101" t="s">
-        <v>168</v>
-      </c>
-      <c r="F101" t="s">
-        <v>10</v>
+        <v>262</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B102" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C102" t="s">
-        <v>169</v>
-      </c>
-      <c r="D102"/>
+        <v>263</v>
+      </c>
+      <c r="D102" t="s">
+        <v>150</v>
+      </c>
       <c r="E102" t="s">
-        <v>170</v>
-      </c>
-      <c r="F102" t="s">
-        <v>10</v>
+        <v>264</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B103" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C103" t="s">
-        <v>171</v>
-      </c>
-      <c r="D103"/>
+        <v>265</v>
+      </c>
+      <c r="D103" t="s">
+        <v>224</v>
+      </c>
       <c r="E103" t="s">
-        <v>172</v>
-      </c>
-      <c r="F103" t="s">
-        <v>10</v>
+        <v>266</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B104" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>173</v>
-      </c>
-      <c r="D104"/>
+        <v>267</v>
+      </c>
+      <c r="D104" t="s">
+        <v>268</v>
+      </c>
       <c r="E104" t="s">
-        <v>174</v>
-      </c>
-      <c r="F104" t="s">
-        <v>10</v>
+        <v>269</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B105" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C105" t="s">
-        <v>175</v>
-      </c>
-      <c r="D105"/>
+        <v>270</v>
+      </c>
+      <c r="D105" t="s">
+        <v>271</v>
+      </c>
       <c r="E105" t="s">
-        <v>176</v>
-      </c>
-      <c r="F105" t="s">
-        <v>10</v>
+        <v>272</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B106" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C106" t="s">
-        <v>177</v>
-      </c>
-      <c r="D106"/>
+        <v>273</v>
+      </c>
+      <c r="D106" t="s">
+        <v>274</v>
+      </c>
       <c r="E106" t="s">
-        <v>178</v>
-      </c>
-      <c r="F106" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B107" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C107" t="s">
-        <v>179</v>
-      </c>
-      <c r="D107"/>
+        <v>275</v>
+      </c>
+      <c r="D107" t="s">
+        <v>276</v>
+      </c>
       <c r="E107" t="s">
-        <v>180</v>
-      </c>
-      <c r="F107" t="s">
-        <v>10</v>
+        <v>277</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B108" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C108" t="s">
-        <v>181</v>
-      </c>
-      <c r="D108"/>
+        <v>278</v>
+      </c>
+      <c r="D108" t="s">
+        <v>279</v>
+      </c>
       <c r="E108" t="s">
-        <v>182</v>
-      </c>
-      <c r="F108" t="s">
-        <v>10</v>
+        <v>280</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B109" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C109" t="s">
-        <v>183</v>
-      </c>
-      <c r="D109"/>
+        <v>281</v>
+      </c>
+      <c r="D109" t="s">
+        <v>282</v>
+      </c>
       <c r="E109" t="s">
-        <v>184</v>
-      </c>
-      <c r="F109" t="s">
-        <v>10</v>
+        <v>283</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B110" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C110" t="s">
-        <v>185</v>
-      </c>
-      <c r="D110"/>
+        <v>284</v>
+      </c>
+      <c r="D110" t="s">
+        <v>285</v>
+      </c>
       <c r="E110" t="s">
-        <v>186</v>
-      </c>
-      <c r="F110" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C111" t="s">
-        <v>187</v>
-      </c>
-      <c r="D111"/>
+        <v>286</v>
+      </c>
+      <c r="D111" t="s">
+        <v>287</v>
+      </c>
       <c r="E111" t="s">
-        <v>188</v>
-      </c>
-      <c r="F111" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C112" t="s">
-        <v>189</v>
-      </c>
-      <c r="D112"/>
+        <v>288</v>
+      </c>
+      <c r="D112" t="s">
+        <v>289</v>
+      </c>
       <c r="E112" t="s">
-        <v>30</v>
-      </c>
-      <c r="F112" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B113" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C113" t="s">
-        <v>190</v>
-      </c>
-      <c r="D113"/>
+        <v>290</v>
+      </c>
+      <c r="D113" t="s">
+        <v>291</v>
+      </c>
       <c r="E113" t="s">
-        <v>191</v>
-      </c>
-      <c r="F113" t="s">
-        <v>10</v>
+        <v>292</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2</v>
+      </c>
+      <c r="G113" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B114" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C114" t="s">
-        <v>192</v>
-      </c>
-      <c r="D114"/>
+        <v>293</v>
+      </c>
+      <c r="D114" t="s">
+        <v>156</v>
+      </c>
       <c r="E114" t="s">
-        <v>193</v>
-      </c>
-      <c r="F114" t="s">
-        <v>10</v>
+        <v>294</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B115" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C115" t="s">
-        <v>194</v>
-      </c>
-      <c r="D115"/>
+        <v>295</v>
+      </c>
+      <c r="D115" t="s">
+        <v>296</v>
+      </c>
       <c r="E115" t="s">
-        <v>195</v>
-      </c>
-      <c r="F115" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B116" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C116" t="s">
-        <v>196</v>
-      </c>
-      <c r="D116"/>
+        <v>297</v>
+      </c>
+      <c r="D116" t="s">
+        <v>298</v>
+      </c>
       <c r="E116" t="s">
-        <v>30</v>
-      </c>
-      <c r="F116" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B117" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C117" t="s">
-        <v>197</v>
-      </c>
-      <c r="D117"/>
+        <v>299</v>
+      </c>
+      <c r="D117" t="s">
+        <v>162</v>
+      </c>
       <c r="E117" t="s">
-        <v>30</v>
-      </c>
-      <c r="F117" t="s">
-        <v>10</v>
+        <v>300</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B118" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C118" t="s">
-        <v>198</v>
-      </c>
-      <c r="D118"/>
+        <v>301</v>
+      </c>
+      <c r="D118" t="s">
+        <v>135</v>
+      </c>
       <c r="E118" t="s">
-        <v>30</v>
-      </c>
-      <c r="F118" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C119" t="s">
-        <v>199</v>
-      </c>
-      <c r="D119"/>
+        <v>302</v>
+      </c>
+      <c r="D119" t="s">
+        <v>303</v>
+      </c>
       <c r="E119" t="s">
-        <v>200</v>
-      </c>
-      <c r="F119" t="s">
-        <v>10</v>
+        <v>304</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B120" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C120" t="s">
-        <v>201</v>
-      </c>
-      <c r="D120"/>
+        <v>305</v>
+      </c>
+      <c r="D120" t="s">
+        <v>306</v>
+      </c>
       <c r="E120" t="s">
-        <v>202</v>
-      </c>
-      <c r="F120" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>203</v>
-      </c>
-      <c r="D121"/>
+        <v>307</v>
+      </c>
+      <c r="D121" t="s">
+        <v>144</v>
+      </c>
       <c r="E121" t="s">
-        <v>30</v>
-      </c>
-      <c r="F121" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F121" t="n">
+        <v>4</v>
+      </c>
+      <c r="G121" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B122" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>204</v>
-      </c>
-      <c r="D122"/>
+        <v>308</v>
+      </c>
+      <c r="D122" t="s">
+        <v>309</v>
+      </c>
       <c r="E122" t="s">
-        <v>30</v>
-      </c>
-      <c r="F122" t="s">
-        <v>10</v>
+        <v>310</v>
+      </c>
+      <c r="F122" t="n">
+        <v>4</v>
+      </c>
+      <c r="G122" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B123" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C123" t="s">
-        <v>205</v>
-      </c>
-      <c r="D123"/>
+        <v>311</v>
+      </c>
+      <c r="D123" t="s">
+        <v>291</v>
+      </c>
       <c r="E123" t="s">
-        <v>206</v>
-      </c>
-      <c r="F123" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F123" t="n">
+        <v>4</v>
+      </c>
+      <c r="G123" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B124" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C124" t="s">
-        <v>207</v>
-      </c>
-      <c r="D124"/>
+        <v>312</v>
+      </c>
+      <c r="D124" t="s">
+        <v>162</v>
+      </c>
       <c r="E124" t="s">
-        <v>30</v>
-      </c>
-      <c r="F124" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F124" t="n">
+        <v>4</v>
+      </c>
+      <c r="G124" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C125" t="s">
-        <v>208</v>
-      </c>
-      <c r="D125"/>
+        <v>313</v>
+      </c>
+      <c r="D125" t="s">
+        <v>314</v>
+      </c>
       <c r="E125" t="s">
-        <v>209</v>
-      </c>
-      <c r="F125" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F125" t="n">
+        <v>4</v>
+      </c>
+      <c r="G125" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C126" t="s">
-        <v>210</v>
-      </c>
-      <c r="D126"/>
+        <v>315</v>
+      </c>
+      <c r="D126" t="s">
+        <v>165</v>
+      </c>
       <c r="E126" t="s">
-        <v>30</v>
-      </c>
-      <c r="F126" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F126" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C127" t="s">
-        <v>211</v>
-      </c>
-      <c r="D127"/>
+        <v>316</v>
+      </c>
+      <c r="D127" t="s">
+        <v>135</v>
+      </c>
       <c r="E127" t="s">
-        <v>30</v>
-      </c>
-      <c r="F127" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F127" t="n">
+        <v>4</v>
+      </c>
+      <c r="G127" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C128" t="s">
-        <v>212</v>
-      </c>
-      <c r="D128"/>
+        <v>317</v>
+      </c>
+      <c r="D128" t="s">
+        <v>306</v>
+      </c>
       <c r="E128" t="s">
-        <v>213</v>
-      </c>
-      <c r="F128" t="s">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B129" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C129" t="s">
-        <v>214</v>
-      </c>
-      <c r="D129"/>
+        <v>318</v>
+      </c>
+      <c r="D129" t="s">
+        <v>319</v>
+      </c>
       <c r="E129" t="s">
-        <v>30</v>
-      </c>
-      <c r="F129" t="s">
-        <v>10</v>
+        <v>320</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C130" t="s">
-        <v>215</v>
-      </c>
-      <c r="D130"/>
+        <v>321</v>
+      </c>
+      <c r="D130" t="s">
+        <v>322</v>
+      </c>
       <c r="E130" t="s">
-        <v>30</v>
-      </c>
-      <c r="F130" t="s">
-        <v>10</v>
+        <v>323</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B131" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C131" t="s">
-        <v>216</v>
-      </c>
-      <c r="D131"/>
+        <v>324</v>
+      </c>
+      <c r="D131" t="s">
+        <v>215</v>
+      </c>
       <c r="E131" t="s">
-        <v>30</v>
-      </c>
-      <c r="F131" t="s">
-        <v>10</v>
+        <v>325</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B132" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C132" t="s">
-        <v>217</v>
-      </c>
-      <c r="D132"/>
+        <v>326</v>
+      </c>
+      <c r="D132" t="s">
+        <v>132</v>
+      </c>
       <c r="E132" t="s">
-        <v>30</v>
-      </c>
-      <c r="F132" t="s">
-        <v>10</v>
+        <v>327</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3</v>
+      </c>
+      <c r="G132" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B133" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C133" t="s">
-        <v>218</v>
-      </c>
-      <c r="D133"/>
+        <v>328</v>
+      </c>
+      <c r="D133" t="s">
+        <v>235</v>
+      </c>
       <c r="E133" t="s">
-        <v>30</v>
-      </c>
-      <c r="F133" t="s">
-        <v>10</v>
+        <v>329</v>
+      </c>
+      <c r="F133" t="n">
+        <v>3</v>
+      </c>
+      <c r="G133" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="C134" t="s">
-        <v>219</v>
-      </c>
-      <c r="D134"/>
+        <v>330</v>
+      </c>
+      <c r="D134" t="s">
+        <v>118</v>
+      </c>
       <c r="E134" t="s">
-        <v>30</v>
-      </c>
-      <c r="F134" t="s">
-        <v>10</v>
+        <v>119</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="C135" t="s">
-        <v>220</v>
-      </c>
-      <c r="D135"/>
+        <v>332</v>
+      </c>
+      <c r="D135" t="s">
+        <v>53</v>
+      </c>
       <c r="E135" t="s">
-        <v>221</v>
-      </c>
-      <c r="F135" t="s">
-        <v>10</v>
+        <v>54</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>222</v>
-      </c>
-      <c r="D136"/>
+        <v>334</v>
+      </c>
+      <c r="D136" t="s">
+        <v>335</v>
+      </c>
       <c r="E136" t="s">
-        <v>223</v>
-      </c>
-      <c r="F136" t="s">
-        <v>10</v>
+        <v>336</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2</v>
+      </c>
+      <c r="G136" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>224</v>
-      </c>
-      <c r="D137"/>
+        <v>337</v>
+      </c>
+      <c r="D137" t="s">
+        <v>97</v>
+      </c>
       <c r="E137" t="s">
-        <v>225</v>
-      </c>
-      <c r="F137" t="s">
-        <v>10</v>
+        <v>338</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>226</v>
-      </c>
-      <c r="D138"/>
+        <v>339</v>
+      </c>
+      <c r="D138" t="s">
+        <v>97</v>
+      </c>
       <c r="E138" t="s">
-        <v>227</v>
-      </c>
-      <c r="F138" t="s">
-        <v>10</v>
+        <v>340</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2</v>
+      </c>
+      <c r="G138" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>228</v>
-      </c>
-      <c r="D139"/>
+        <v>341</v>
+      </c>
+      <c r="D139" t="s">
+        <v>37</v>
+      </c>
       <c r="E139" t="s">
-        <v>229</v>
-      </c>
-      <c r="F139" t="s">
-        <v>10</v>
+        <v>38</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2</v>
+      </c>
+      <c r="G139" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>230</v>
+        <v>342</v>
       </c>
       <c r="D140" t="s">
-        <v>231</v>
+        <v>343</v>
       </c>
       <c r="E140" t="s">
-        <v>232</v>
-      </c>
-      <c r="F140" t="s">
-        <v>233</v>
+        <v>344</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B141" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C141" t="s">
-        <v>234</v>
+        <v>345</v>
       </c>
       <c r="D141" t="s">
-        <v>231</v>
+        <v>147</v>
       </c>
       <c r="E141" t="s">
-        <v>235</v>
-      </c>
-      <c r="F141" t="s">
-        <v>233</v>
+        <v>148</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B142" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C142" t="s">
-        <v>236</v>
+        <v>346</v>
       </c>
       <c r="D142" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="E142" t="s">
-        <v>37</v>
-      </c>
-      <c r="F142" t="s">
-        <v>233</v>
+        <v>142</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B143" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C143" t="s">
-        <v>238</v>
+        <v>347</v>
       </c>
       <c r="D143" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="E143" t="s">
-        <v>83</v>
-      </c>
-      <c r="F143" t="s">
-        <v>233</v>
+        <v>348</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B144" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C144" t="s">
-        <v>31</v>
+        <v>349</v>
       </c>
       <c r="D144" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="E144" t="s">
-        <v>32</v>
-      </c>
-      <c r="F144" t="s">
-        <v>233</v>
+        <v>350</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B145" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C145" t="s">
-        <v>241</v>
+        <v>351</v>
       </c>
       <c r="D145" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="E145" t="s">
-        <v>243</v>
-      </c>
-      <c r="F145" t="s">
-        <v>233</v>
+        <v>352</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B146" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C146" t="s">
-        <v>244</v>
+        <v>353</v>
       </c>
       <c r="D146" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="E146" t="s">
-        <v>26</v>
-      </c>
-      <c r="F146" t="s">
-        <v>233</v>
+        <v>160</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B147" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C147" t="s">
-        <v>11</v>
+        <v>354</v>
       </c>
       <c r="D147" t="s">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="E147" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" t="s">
-        <v>233</v>
+        <v>187</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>8</v>
+        <v>355</v>
       </c>
       <c r="D148" t="s">
-        <v>247</v>
+        <v>40</v>
       </c>
       <c r="E148" t="s">
-        <v>9</v>
-      </c>
-      <c r="F148" t="s">
-        <v>233</v>
+        <v>356</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>248</v>
+        <v>358</v>
       </c>
       <c r="D149" t="s">
-        <v>249</v>
+        <v>49</v>
       </c>
       <c r="E149" t="s">
-        <v>250</v>
-      </c>
-      <c r="F149" t="s">
-        <v>233</v>
+        <v>359</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B150" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>54</v>
+        <v>360</v>
       </c>
       <c r="D150" t="s">
-        <v>251</v>
+        <v>31</v>
       </c>
       <c r="E150" t="s">
-        <v>55</v>
-      </c>
-      <c r="F150" t="s">
-        <v>233</v>
+        <v>361</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B151" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C151" t="s">
-        <v>19</v>
+        <v>362</v>
       </c>
       <c r="D151" t="s">
-        <v>252</v>
+        <v>363</v>
       </c>
       <c r="E151" t="s">
-        <v>253</v>
-      </c>
-      <c r="F151" t="s">
-        <v>233</v>
+        <v>364</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="B152" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C152" t="s">
-        <v>23</v>
+        <v>365</v>
       </c>
       <c r="D152" t="s">
-        <v>254</v>
+        <v>366</v>
       </c>
       <c r="E152" t="s">
-        <v>255</v>
-      </c>
-      <c r="F152" t="s">
-        <v>233</v>
+        <v>367</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B153" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C153" t="s">
-        <v>256</v>
+        <v>368</v>
       </c>
       <c r="D153" t="s">
-        <v>257</v>
-      </c>
-      <c r="E153"/>
-      <c r="F153" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>88</v>
-      </c>
-      <c r="B154" t="s">
-        <v>89</v>
-      </c>
-      <c r="C154" t="s">
-        <v>258</v>
-      </c>
-      <c r="D154" t="s">
-        <v>259</v>
-      </c>
-      <c r="E154" t="s">
-        <v>260</v>
-      </c>
-      <c r="F154" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>88</v>
-      </c>
-      <c r="B155" t="s">
-        <v>89</v>
-      </c>
-      <c r="C155" t="s">
-        <v>261</v>
-      </c>
-      <c r="D155" t="s">
-        <v>262</v>
-      </c>
-      <c r="E155" t="s">
-        <v>110</v>
-      </c>
-      <c r="F155" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>88</v>
-      </c>
-      <c r="B156" t="s">
-        <v>89</v>
-      </c>
-      <c r="C156" t="s">
-        <v>263</v>
-      </c>
-      <c r="D156" t="s">
-        <v>264</v>
-      </c>
-      <c r="E156" t="s">
-        <v>128</v>
-      </c>
-      <c r="F156" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>88</v>
-      </c>
-      <c r="B157" t="s">
-        <v>89</v>
-      </c>
-      <c r="C157" t="s">
-        <v>92</v>
-      </c>
-      <c r="D157" t="s">
-        <v>265</v>
-      </c>
-      <c r="E157" t="s">
-        <v>93</v>
-      </c>
-      <c r="F157" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>88</v>
-      </c>
-      <c r="B158" t="s">
-        <v>89</v>
-      </c>
-      <c r="C158" t="s">
-        <v>90</v>
-      </c>
-      <c r="D158" t="s">
-        <v>266</v>
-      </c>
-      <c r="E158" t="s">
-        <v>91</v>
-      </c>
-      <c r="F158" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>88</v>
-      </c>
-      <c r="B159" t="s">
-        <v>89</v>
-      </c>
-      <c r="C159" t="s">
-        <v>267</v>
-      </c>
-      <c r="D159" t="s">
-        <v>268</v>
-      </c>
-      <c r="E159" t="s">
-        <v>102</v>
-      </c>
-      <c r="F159" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>88</v>
-      </c>
-      <c r="B160" t="s">
-        <v>89</v>
-      </c>
-      <c r="C160" t="s">
-        <v>269</v>
-      </c>
-      <c r="D160" t="s">
-        <v>270</v>
-      </c>
-      <c r="E160" t="s">
-        <v>98</v>
-      </c>
-      <c r="F160" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>88</v>
-      </c>
-      <c r="B161" t="s">
-        <v>89</v>
-      </c>
-      <c r="C161" t="s">
-        <v>271</v>
-      </c>
-      <c r="D161" t="s">
-        <v>272</v>
-      </c>
-      <c r="E161" t="s">
-        <v>273</v>
-      </c>
-      <c r="F161" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>6</v>
-      </c>
-      <c r="B162" t="s">
-        <v>7</v>
-      </c>
-      <c r="C162" t="s">
-        <v>230</v>
-      </c>
-      <c r="D162" t="s">
-        <v>231</v>
-      </c>
-      <c r="E162" t="s">
-        <v>232</v>
-      </c>
-      <c r="F162" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>6</v>
-      </c>
-      <c r="B163" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163" t="s">
-        <v>234</v>
-      </c>
-      <c r="D163" t="s">
-        <v>231</v>
-      </c>
-      <c r="E163" t="s">
-        <v>235</v>
-      </c>
-      <c r="F163" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>6</v>
-      </c>
-      <c r="B164" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" t="s">
-        <v>236</v>
-      </c>
-      <c r="D164" t="s">
-        <v>237</v>
-      </c>
-      <c r="E164" t="s">
-        <v>37</v>
-      </c>
-      <c r="F164" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>6</v>
-      </c>
-      <c r="B165" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" t="s">
-        <v>31</v>
-      </c>
-      <c r="D165" t="s">
-        <v>240</v>
-      </c>
-      <c r="E165" t="s">
-        <v>32</v>
-      </c>
-      <c r="F165" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>6</v>
-      </c>
-      <c r="B166" t="s">
-        <v>7</v>
-      </c>
-      <c r="C166" t="s">
-        <v>241</v>
-      </c>
-      <c r="D166" t="s">
-        <v>242</v>
-      </c>
-      <c r="E166" t="s">
-        <v>243</v>
-      </c>
-      <c r="F166" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>6</v>
-      </c>
-      <c r="B167" t="s">
-        <v>7</v>
-      </c>
-      <c r="C167" t="s">
-        <v>244</v>
-      </c>
-      <c r="D167" t="s">
-        <v>245</v>
-      </c>
-      <c r="E167" t="s">
-        <v>26</v>
-      </c>
-      <c r="F167" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>6</v>
-      </c>
-      <c r="B168" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" t="s">
-        <v>11</v>
-      </c>
-      <c r="D168" t="s">
-        <v>246</v>
-      </c>
-      <c r="E168" t="s">
-        <v>12</v>
-      </c>
-      <c r="F168" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" t="s">
-        <v>8</v>
-      </c>
-      <c r="D169" t="s">
-        <v>247</v>
-      </c>
-      <c r="E169" t="s">
-        <v>9</v>
-      </c>
-      <c r="F169" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>88</v>
-      </c>
-      <c r="B170" t="s">
-        <v>89</v>
-      </c>
-      <c r="C170" t="s">
-        <v>92</v>
-      </c>
-      <c r="D170" t="s">
-        <v>265</v>
-      </c>
-      <c r="E170" t="s">
-        <v>93</v>
-      </c>
-      <c r="F170" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>6</v>
-      </c>
-      <c r="B171" t="s">
-        <v>7</v>
-      </c>
-      <c r="C171" t="s">
-        <v>90</v>
-      </c>
-      <c r="D171" t="s">
-        <v>266</v>
-      </c>
-      <c r="E171" t="s">
-        <v>91</v>
-      </c>
-      <c r="F171" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>6</v>
-      </c>
-      <c r="B172" t="s">
-        <v>7</v>
-      </c>
-      <c r="C172" t="s">
-        <v>275</v>
-      </c>
-      <c r="D172" t="s">
-        <v>276</v>
-      </c>
-      <c r="E172" t="s">
-        <v>277</v>
-      </c>
-      <c r="F172" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>6</v>
-      </c>
-      <c r="B173" t="s">
-        <v>7</v>
-      </c>
-      <c r="C173" t="s">
-        <v>278</v>
-      </c>
-      <c r="D173" t="s">
-        <v>279</v>
-      </c>
-      <c r="E173" t="s">
-        <v>280</v>
-      </c>
-      <c r="F173" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>6</v>
-      </c>
-      <c r="B174" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" t="s">
-        <v>281</v>
-      </c>
-      <c r="D174" t="s">
-        <v>282</v>
-      </c>
-      <c r="E174" t="s">
-        <v>283</v>
-      </c>
-      <c r="F174" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>6</v>
-      </c>
-      <c r="B175" t="s">
-        <v>7</v>
-      </c>
-      <c r="C175" t="s">
-        <v>284</v>
-      </c>
-      <c r="D175" t="s">
-        <v>251</v>
-      </c>
-      <c r="E175" t="s">
-        <v>55</v>
-      </c>
-      <c r="F175" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>6</v>
-      </c>
-      <c r="B176" t="s">
-        <v>7</v>
-      </c>
-      <c r="C176" t="s">
-        <v>285</v>
-      </c>
-      <c r="D176"/>
-      <c r="E176"/>
-      <c r="F176" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" t="s">
-        <v>7</v>
-      </c>
-      <c r="C177" t="s">
-        <v>286</v>
-      </c>
-      <c r="D177"/>
-      <c r="E177"/>
-      <c r="F177" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>6</v>
-      </c>
-      <c r="B178" t="s">
-        <v>7</v>
-      </c>
-      <c r="C178" t="s">
-        <v>287</v>
-      </c>
-      <c r="D178"/>
-      <c r="E178"/>
-      <c r="F178" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>6</v>
-      </c>
-      <c r="B179" t="s">
-        <v>7</v>
-      </c>
-      <c r="C179" t="s">
-        <v>288</v>
-      </c>
-      <c r="D179"/>
-      <c r="E179"/>
-      <c r="F179" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>6</v>
-      </c>
-      <c r="B180" t="s">
-        <v>7</v>
-      </c>
-      <c r="C180" t="s">
-        <v>289</v>
-      </c>
-      <c r="D180"/>
-      <c r="E180"/>
-      <c r="F180" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>6</v>
-      </c>
-      <c r="B181" t="s">
-        <v>7</v>
-      </c>
-      <c r="C181" t="s">
-        <v>285</v>
-      </c>
-      <c r="D181"/>
-      <c r="E181"/>
-      <c r="F181" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>6</v>
-      </c>
-      <c r="B182" t="s">
-        <v>7</v>
-      </c>
-      <c r="C182" t="s">
-        <v>290</v>
-      </c>
-      <c r="D182"/>
-      <c r="E182"/>
-      <c r="F182" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>6</v>
-      </c>
-      <c r="B183" t="s">
-        <v>7</v>
-      </c>
-      <c r="C183" t="s">
-        <v>291</v>
-      </c>
-      <c r="D183"/>
-      <c r="E183"/>
-      <c r="F183" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>88</v>
-      </c>
-      <c r="B184" t="s">
-        <v>89</v>
-      </c>
-      <c r="C184" t="s">
-        <v>292</v>
-      </c>
-      <c r="D184" t="s">
-        <v>293</v>
-      </c>
-      <c r="E184" t="s">
-        <v>206</v>
-      </c>
-      <c r="F184" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>88</v>
-      </c>
-      <c r="B185" t="s">
-        <v>89</v>
-      </c>
-      <c r="C185" t="s">
-        <v>294</v>
-      </c>
-      <c r="D185" t="s">
-        <v>295</v>
-      </c>
-      <c r="E185" t="s">
-        <v>296</v>
-      </c>
-      <c r="F185" t="s">
-        <v>274</v>
+        <v>369</v>
+      </c>
+      <c r="E153" t="s">
+        <v>163</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
